--- a/XBRL-template-MFRS/08-SOCF-Direct.xlsx
+++ b/XBRL-template-MFRS/08-SOCF-Direct.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -67,8 +67,21 @@
       <family val="0"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -91,6 +104,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
         <bgColor rgb="FFD6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6E4F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -128,7 +146,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -183,6 +201,18 @@
     </xf>
     <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -445,12 +475,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="10">
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="22" t="inlineStr">
         <is>
           <t>01/01/YYYY - 31/12/YYYY</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="22" t="inlineStr">
         <is>
           <t>01/01/YYYY - 31/12/YYYY</t>
         </is>
@@ -469,8 +499,8 @@
           <t>Statement of cash flows [abstract]</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n"/>
-      <c r="C4" s="14" t="n"/>
+      <c r="B4" s="20" t="n"/>
+      <c r="C4" s="20" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="10">
       <c r="A5" s="13" t="inlineStr">
@@ -478,8 +508,8 @@
           <t>Statement of cash flows [line items]</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n"/>
-      <c r="C5" s="14" t="n"/>
+      <c r="B5" s="20" t="n"/>
+      <c r="C5" s="20" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1" s="10">
       <c r="A6" s="13" t="inlineStr">
@@ -487,8 +517,8 @@
           <t>Statement of cash flows [abstract]</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n"/>
-      <c r="C6" s="14" t="n"/>
+      <c r="B6" s="20" t="n"/>
+      <c r="C6" s="20" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="10">
       <c r="A7" s="13" t="inlineStr">
@@ -496,8 +526,8 @@
           <t>Cash flows from (used in) operating activities [abstract]</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n"/>
-      <c r="C7" s="14" t="n"/>
+      <c r="B7" s="20" t="n"/>
+      <c r="C7" s="20" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="10">
       <c r="A8" s="15" t="inlineStr">
@@ -613,11 +643,11 @@
           <t>Net cash flows from (used in) operating activities</t>
         </is>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="21">
         <f>1*B8+1*B9+1*B10+1*B11+-1*B12+-1*B13+1*B14+-1*B15+1*B16+-1*B17+-1*B18+1*B19</f>
         <v/>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="21">
         <f>1*C8+1*C9+1*C10+1*C11+-1*C12+-1*C13+1*C14+-1*C15+1*C16+-1*C17+-1*C18+1*C19</f>
         <v/>
       </c>
@@ -628,8 +658,8 @@
           <t>Cash flows from (used in) investing activities [abstract]</t>
         </is>
       </c>
-      <c r="B21" s="14" t="n"/>
-      <c r="C21" s="14" t="n"/>
+      <c r="B21" s="20" t="n"/>
+      <c r="C21" s="20" t="n"/>
     </row>
     <row r="22" ht="23.85" customHeight="1" s="10">
       <c r="A22" s="15" t="inlineStr">
@@ -907,11 +937,11 @@
           <t>Net cash flows from (used in) investing activities</t>
         </is>
       </c>
-      <c r="B52" s="16">
+      <c r="B52" s="21">
         <f>1*B22+-1*B23+1*B24+-1*B25+1*B26+-1*B27+1*B28+-1*B29+-1*B30+-1*B31+1*B32+1*B33+-1*B34+1*B35+1*B36+1*B37+1*B38+1*B39+-1*B40+-1*B41+-1*B42+1*B43+1*B44+1*B45+-1*B46+-1*B47+1*B48+1*B49+1*B50+1*B51</f>
         <v/>
       </c>
-      <c r="C52" s="16">
+      <c r="C52" s="21">
         <f>1*C22+-1*C23+1*C24+-1*C25+1*C26+-1*C27+1*C28+-1*C29+-1*C30+-1*C31+1*C32+1*C33+-1*C34+1*C35+1*C36+1*C37+1*C38+1*C39+-1*C40+-1*C41+-1*C42+1*C43+1*C44+1*C45+-1*C46+-1*C47+1*C48+1*C49+1*C50+1*C51</f>
         <v/>
       </c>
@@ -922,8 +952,8 @@
           <t>Cash flows from (used in) financing activities [abstract]</t>
         </is>
       </c>
-      <c r="B53" s="14" t="n"/>
-      <c r="C53" s="14" t="n"/>
+      <c r="B53" s="20" t="n"/>
+      <c r="C53" s="20" t="n"/>
     </row>
     <row r="54" ht="15" customHeight="1" s="10">
       <c r="A54" s="15" t="inlineStr">
@@ -1093,11 +1123,11 @@
           <t>Net cash flows from (used in) financing activities</t>
         </is>
       </c>
-      <c r="B72" s="16">
+      <c r="B72" s="21">
         <f>-1*B54+-1*B55+1*B56+1*B57+1*B58+1*B59+-1*B60+-1*B61+-1*B62+-1*B63+1*B64+-1*B65+-1*B66+1*B67+1*B68+-1*B69+-1*B70+1*B71</f>
         <v/>
       </c>
-      <c r="C72" s="16">
+      <c r="C72" s="21">
         <f>-1*C54+-1*C55+1*C56+1*C57+1*C58+1*C59+-1*C60+-1*C61+-1*C62+-1*C63+1*C64+-1*C65+-1*C66+1*C67+1*C68+-1*C69+-1*C70+1*C71</f>
         <v/>
       </c>
@@ -1108,11 +1138,11 @@
           <t>Net increase (decrease) in cash and cash equivalents before effect of exchange rate changes</t>
         </is>
       </c>
-      <c r="B73" s="16">
+      <c r="B73" s="21">
         <f>1*B20+1*B52+1*B72</f>
         <v/>
       </c>
-      <c r="C73" s="16">
+      <c r="C73" s="21">
         <f>1*C20+1*C52+1*C72</f>
         <v/>
       </c>
@@ -1132,11 +1162,11 @@
           <t>Net increase (decrease) in cash and cash equivalents after effect of exchange rate changes</t>
         </is>
       </c>
-      <c r="B75" s="16">
+      <c r="B75" s="21">
         <f>1*B73+1*B74</f>
         <v/>
       </c>
-      <c r="C75" s="16">
+      <c r="C75" s="21">
         <f>1*C73+1*C74</f>
         <v/>
       </c>
@@ -1156,11 +1186,11 @@
           <t>Cash and cash equivalents at end of period</t>
         </is>
       </c>
-      <c r="B77" s="16">
+      <c r="B77" s="21">
         <f>1*B76+1*B75</f>
         <v/>
       </c>
-      <c r="C77" s="16">
+      <c r="C77" s="21">
         <f>1*C76+1*C75</f>
         <v/>
       </c>
@@ -1171,8 +1201,8 @@
           <t>Details of cash flows [abstract]</t>
         </is>
       </c>
-      <c r="B78" s="14" t="n"/>
-      <c r="C78" s="14" t="n"/>
+      <c r="B78" s="20" t="n"/>
+      <c r="C78" s="20" t="n"/>
     </row>
     <row r="79" ht="15" customHeight="1" s="10">
       <c r="A79" s="17" t="inlineStr">

--- a/XBRL-template-MFRS/08-SOCF-Direct.xlsx
+++ b/XBRL-template-MFRS/08-SOCF-Direct.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="11">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
+  </numFmts>
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -80,8 +82,48 @@
       <name val="Arial"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -111,8 +153,26 @@
         <fgColor rgb="FFD6E4F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+        <bgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF2F8"/>
+        <bgColor rgb="00EEF2F8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -135,6 +195,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="001F3864"/>
+      </bottom>
+    </border>
+    <border/>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D9DEE5"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="001F3864"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="001F3864"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -146,7 +225,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -213,6 +292,42 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -467,784 +582,871 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C82"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="55" customWidth="1" style="9" min="1" max="1"/>
-    <col width="22" customWidth="1" style="9" min="2" max="3"/>
+    <col width="18" customWidth="1" style="9" min="2" max="3"/>
+    <col width="18" customWidth="1" style="10" min="3" max="3"/>
+    <col width="40" customWidth="1" style="10" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="10">
-      <c r="B1" s="22" t="inlineStr">
+    <row r="1" ht="20" customHeight="1" s="10">
+      <c r="B1" s="23" t="inlineStr">
         <is>
           <t>01/01/YYYY - 31/12/YYYY</t>
         </is>
       </c>
-      <c r="C1" s="22" t="inlineStr">
+      <c r="C1" s="23" t="inlineStr">
         <is>
           <t>01/01/YYYY - 31/12/YYYY</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="10">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="D1" s="31" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" s="10">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>Statement of cash flows, direct method</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="10">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="D3" s="24" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="10">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Statement of cash flows [abstract]</t>
         </is>
       </c>
-      <c r="B4" s="20" t="n"/>
-      <c r="C4" s="20" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="10">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="B4" s="26" t="n"/>
+      <c r="C4" s="26" t="n"/>
+      <c r="D4" s="32" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1" s="10">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Statement of cash flows [line items]</t>
         </is>
       </c>
-      <c r="B5" s="20" t="n"/>
-      <c r="C5" s="20" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="10">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="32" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="10">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Statement of cash flows [abstract]</t>
         </is>
       </c>
-      <c r="B6" s="20" t="n"/>
-      <c r="C6" s="20" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="10">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="B6" s="26" t="n"/>
+      <c r="C6" s="26" t="n"/>
+      <c r="D6" s="32" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1" s="10">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Cash flows from (used in) operating activities [abstract]</t>
         </is>
       </c>
-      <c r="B7" s="20" t="n"/>
-      <c r="C7" s="20" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="10">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="B7" s="26" t="n"/>
+      <c r="C7" s="26" t="n"/>
+      <c r="D7" s="32" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1" s="10">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>Receipts from sales of goods and rendering of services</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="10">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="B8" s="28" t="n"/>
+      <c r="C8" s="28" t="n"/>
+      <c r="D8" s="33" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="10">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>Receipts from royalties, fees, commissions and other revenue</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="B9" s="28" t="n"/>
+      <c r="C9" s="28" t="n"/>
+      <c r="D9" s="33" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1" s="10">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>Receipts from contracts held for dealing or trading purposes</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-    </row>
-    <row r="11" ht="35.05" customHeight="1" s="10">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="B10" s="28" t="n"/>
+      <c r="C10" s="28" t="n"/>
+      <c r="D10" s="33" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" s="10">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>Short-term lease payments, payments for leases of low-value assets and variable lease payments not included in the measurement of the lease liability</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="10">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="B11" s="28" t="n"/>
+      <c r="C11" s="28" t="n"/>
+      <c r="D11" s="33" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1" s="10">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Payments to suppliers for goods and services</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="10">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="B12" s="28" t="n"/>
+      <c r="C12" s="28" t="n"/>
+      <c r="D12" s="33" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1" s="10">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>Payments to and on behalf of employees</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="10">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="B13" s="28" t="n"/>
+      <c r="C13" s="28" t="n"/>
+      <c r="D13" s="33" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1" s="10">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>Dividends received</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="10">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="B14" s="28" t="n"/>
+      <c r="C14" s="28" t="n"/>
+      <c r="D14" s="33" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1" s="10">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>Dividends paid</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="10">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="B15" s="28" t="n"/>
+      <c r="C15" s="28" t="n"/>
+      <c r="D15" s="33" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1" s="10">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>Interest received</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="10">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="B16" s="28" t="n"/>
+      <c r="C16" s="28" t="n"/>
+      <c r="D16" s="33" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1" s="10">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>Interest paid</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="10">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="B17" s="28" t="n"/>
+      <c r="C17" s="28" t="n"/>
+      <c r="D17" s="33" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1" s="10">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>Income taxes refund (paid)</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="10">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="B18" s="28" t="n"/>
+      <c r="C18" s="28" t="n"/>
+      <c r="D18" s="33" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1" s="10">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>Other inflows (outflows) of cash, classified as operating activities</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="10">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="B19" s="28" t="n"/>
+      <c r="C19" s="28" t="n"/>
+      <c r="D19" s="33" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1" s="10">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>Net cash flows from (used in) operating activities</t>
         </is>
       </c>
-      <c r="B20" s="21">
+      <c r="B20" s="28">
         <f>1*B8+1*B9+1*B10+1*B11+-1*B12+-1*B13+1*B14+-1*B15+1*B16+-1*B17+-1*B18+1*B19</f>
         <v/>
       </c>
-      <c r="C20" s="21">
+      <c r="C20" s="28">
         <f>1*C8+1*C9+1*C10+1*C11+-1*C12+-1*C13+1*C14+-1*C15+1*C16+-1*C17+-1*C18+1*C19</f>
         <v/>
       </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="10">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="D20" s="33" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1" s="10">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>Cash flows from (used in) investing activities [abstract]</t>
         </is>
       </c>
-      <c r="B21" s="20" t="n"/>
-      <c r="C21" s="20" t="n"/>
-    </row>
-    <row r="22" ht="23.85" customHeight="1" s="10">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="B21" s="26" t="n"/>
+      <c r="C21" s="26" t="n"/>
+      <c r="D21" s="32" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1" s="10">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>Cash flows from losing control of subsidiaries or other businesses, classified as investing activities</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
-    </row>
-    <row r="23" ht="23.85" customHeight="1" s="10">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="B22" s="28" t="n"/>
+      <c r="C22" s="28" t="n"/>
+      <c r="D22" s="33" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1" s="10">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>Cash flows used in obtaining control of subsidiaries or other businesses, classified as investing activities</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n"/>
-      <c r="C23" s="16" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="10">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="B23" s="28" t="n"/>
+      <c r="C23" s="28" t="n"/>
+      <c r="D23" s="33" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1" s="10">
+      <c r="A24" s="27" t="inlineStr">
         <is>
           <t>Proceeds from sales of interests in associates</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="16" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="10">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="B24" s="28" t="n"/>
+      <c r="C24" s="28" t="n"/>
+      <c r="D24" s="33" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1" s="10">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>Purchase of interests in associates</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-    </row>
-    <row r="26" ht="23.85" customHeight="1" s="10">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="B25" s="28" t="n"/>
+      <c r="C25" s="28" t="n"/>
+      <c r="D25" s="33" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1" s="10">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>Other cash receipts from sales of interests in joint ventures, classified as investing activities</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="16" t="n"/>
-    </row>
-    <row r="27" ht="23.85" customHeight="1" s="10">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="B26" s="28" t="n"/>
+      <c r="C26" s="28" t="n"/>
+      <c r="D26" s="33" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1" s="10">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>Other cash payments to acquire interests in joint ventures, classified as investing activities</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="16" t="n"/>
-    </row>
-    <row r="28" ht="23.85" customHeight="1" s="10">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="B27" s="28" t="n"/>
+      <c r="C27" s="28" t="n"/>
+      <c r="D27" s="33" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1" s="10">
+      <c r="A28" s="27" t="inlineStr">
         <is>
           <t>Cash receipts from repayment of advances and loans made to other parties, classified as investing activities</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="10">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="B28" s="28" t="n"/>
+      <c r="C28" s="28" t="n"/>
+      <c r="D28" s="33" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1" s="10">
+      <c r="A29" s="27" t="inlineStr">
         <is>
           <t>Cash advances and loans made to other parties</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="16" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="10">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="B29" s="28" t="n"/>
+      <c r="C29" s="28" t="n"/>
+      <c r="D29" s="33" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1" s="10">
+      <c r="A30" s="27" t="inlineStr">
         <is>
           <t>Deposit placed with investment brokers</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="16" t="n"/>
-    </row>
-    <row r="31" ht="23.85" customHeight="1" s="10">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="B30" s="28" t="n"/>
+      <c r="C30" s="28" t="n"/>
+      <c r="D30" s="33" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1" s="10">
+      <c r="A31" s="27" t="inlineStr">
         <is>
           <t>Other cash payments to acquire equity or debt instruments of other entities</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="16" t="n"/>
-    </row>
-    <row r="32" ht="23.85" customHeight="1" s="10">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="B31" s="28" t="n"/>
+      <c r="C31" s="28" t="n"/>
+      <c r="D31" s="33" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1" s="10">
+      <c r="A32" s="27" t="inlineStr">
         <is>
           <t>Other cash receipts from sales of equity or debt instruments of other entities, classified as investing activities</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n"/>
-      <c r="C32" s="16" t="n"/>
-    </row>
-    <row r="33" ht="23.85" customHeight="1" s="10">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="B32" s="28" t="n"/>
+      <c r="C32" s="28" t="n"/>
+      <c r="D32" s="33" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1" s="10">
+      <c r="A33" s="27" t="inlineStr">
         <is>
           <t>Proceeds from disposal of net cash and cash equivalents disposed off</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="16" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="10">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="B33" s="28" t="n"/>
+      <c r="C33" s="28" t="n"/>
+      <c r="D33" s="33" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1" s="10">
+      <c r="A34" s="27" t="inlineStr">
         <is>
           <t>Tax paid on gain on disposal from discontinuing operations</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="16" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="10">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="B34" s="28" t="n"/>
+      <c r="C34" s="28" t="n"/>
+      <c r="D34" s="33" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1" s="10">
+      <c r="A35" s="27" t="inlineStr">
         <is>
           <t>Proceeds from government grants</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="10">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="B35" s="28" t="n"/>
+      <c r="C35" s="28" t="n"/>
+      <c r="D35" s="33" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1" s="10">
+      <c r="A36" s="27" t="inlineStr">
         <is>
           <t>Proceeds from sales of intangible assets</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="16" t="n"/>
-    </row>
-    <row r="37" ht="23.85" customHeight="1" s="10">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="B36" s="28" t="n"/>
+      <c r="C36" s="28" t="n"/>
+      <c r="D36" s="33" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1" s="10">
+      <c r="A37" s="27" t="inlineStr">
         <is>
           <t>Proceeds from sales of other long-term assets, classified as investing activities</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n"/>
-      <c r="C37" s="16" t="n"/>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="10">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="B37" s="28" t="n"/>
+      <c r="C37" s="28" t="n"/>
+      <c r="D37" s="33" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1" s="10">
+      <c r="A38" s="27" t="inlineStr">
         <is>
           <t>Proceeds from sales of property, plant and equipment</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n"/>
-      <c r="C38" s="16" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="10">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="B38" s="28" t="n"/>
+      <c r="C38" s="28" t="n"/>
+      <c r="D38" s="33" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1" s="10">
+      <c r="A39" s="27" t="inlineStr">
         <is>
           <t>Proceeds from sale of prepaid lease payments</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n"/>
-      <c r="C39" s="16" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="10">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="B39" s="28" t="n"/>
+      <c r="C39" s="28" t="n"/>
+      <c r="D39" s="33" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1" s="10">
+      <c r="A40" s="27" t="inlineStr">
         <is>
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n"/>
-      <c r="C40" s="16" t="n"/>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="10">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="B40" s="28" t="n"/>
+      <c r="C40" s="28" t="n"/>
+      <c r="D40" s="33" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1" s="10">
+      <c r="A41" s="27" t="inlineStr">
         <is>
           <t>Purchase of other non-current assets</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="n"/>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="10">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="B41" s="28" t="n"/>
+      <c r="C41" s="28" t="n"/>
+      <c r="D41" s="33" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1" s="10">
+      <c r="A42" s="27" t="inlineStr">
         <is>
           <t>Purchase of property, plant and equipment</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="n"/>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="10">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="B42" s="28" t="n"/>
+      <c r="C42" s="28" t="n"/>
+      <c r="D42" s="33" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1" s="10">
+      <c r="A43" s="27" t="inlineStr">
         <is>
           <t>Dividends received</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="16" t="n"/>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="10">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="B43" s="28" t="n"/>
+      <c r="C43" s="28" t="n"/>
+      <c r="D43" s="33" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1" s="10">
+      <c r="A44" s="27" t="inlineStr">
         <is>
           <t>Interest received</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n"/>
-      <c r="C44" s="16" t="n"/>
-    </row>
-    <row r="45" ht="23.85" customHeight="1" s="10">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="B44" s="28" t="n"/>
+      <c r="C44" s="28" t="n"/>
+      <c r="D44" s="33" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1" s="10">
+      <c r="A45" s="27" t="inlineStr">
         <is>
           <t>Proceeds from sales of investments other than investments accounted for using equity method</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="16" t="n"/>
-    </row>
-    <row r="46" ht="15" customHeight="1" s="10">
-      <c r="A46" s="15" t="inlineStr">
+      <c r="B45" s="28" t="n"/>
+      <c r="C45" s="28" t="n"/>
+      <c r="D45" s="33" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1" s="10">
+      <c r="A46" s="27" t="inlineStr">
         <is>
           <t>Purchase of other investment</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="n"/>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="10">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="B46" s="28" t="n"/>
+      <c r="C46" s="28" t="n"/>
+      <c r="D46" s="33" t="n"/>
+    </row>
+    <row r="47" ht="18" customHeight="1" s="10">
+      <c r="A47" s="27" t="inlineStr">
         <is>
           <t>Development expenditure incurred</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n"/>
-      <c r="C47" s="16" t="n"/>
-    </row>
-    <row r="48" ht="15" customHeight="1" s="10">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="B47" s="28" t="n"/>
+      <c r="C47" s="28" t="n"/>
+      <c r="D47" s="33" t="n"/>
+    </row>
+    <row r="48" ht="18" customHeight="1" s="10">
+      <c r="A48" s="27" t="inlineStr">
         <is>
           <t>Net repayment from joint ventures</t>
         </is>
       </c>
-      <c r="B48" s="16" t="n"/>
-      <c r="C48" s="16" t="n"/>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="10">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="B48" s="28" t="n"/>
+      <c r="C48" s="28" t="n"/>
+      <c r="D48" s="33" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1" s="10">
+      <c r="A49" s="27" t="inlineStr">
         <is>
           <t>Net repayment from associates</t>
         </is>
       </c>
-      <c r="B49" s="16" t="n"/>
-      <c r="C49" s="16" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1" s="10">
-      <c r="A50" s="15" t="inlineStr">
+      <c r="B49" s="28" t="n"/>
+      <c r="C49" s="28" t="n"/>
+      <c r="D49" s="33" t="n"/>
+    </row>
+    <row r="50" ht="18" customHeight="1" s="10">
+      <c r="A50" s="27" t="inlineStr">
         <is>
           <t>Capital distributions from associates</t>
         </is>
       </c>
-      <c r="B50" s="16" t="n"/>
-      <c r="C50" s="16" t="n"/>
-    </row>
-    <row r="51" ht="15" customHeight="1" s="10">
-      <c r="A51" s="15" t="inlineStr">
+      <c r="B50" s="28" t="n"/>
+      <c r="C50" s="28" t="n"/>
+      <c r="D50" s="33" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1" s="10">
+      <c r="A51" s="27" t="inlineStr">
         <is>
           <t>Other inflows (outflows) of cash, classified as investing activities</t>
         </is>
       </c>
-      <c r="B51" s="16" t="n"/>
-      <c r="C51" s="16" t="n"/>
-    </row>
-    <row r="52" ht="15" customHeight="1" s="10">
-      <c r="A52" s="15" t="inlineStr">
+      <c r="B51" s="28" t="n"/>
+      <c r="C51" s="28" t="n"/>
+      <c r="D51" s="33" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1" s="10">
+      <c r="A52" s="27" t="inlineStr">
         <is>
           <t>Net cash flows from (used in) investing activities</t>
         </is>
       </c>
-      <c r="B52" s="21">
+      <c r="B52" s="28">
         <f>1*B22+-1*B23+1*B24+-1*B25+1*B26+-1*B27+1*B28+-1*B29+-1*B30+-1*B31+1*B32+1*B33+-1*B34+1*B35+1*B36+1*B37+1*B38+1*B39+-1*B40+-1*B41+-1*B42+1*B43+1*B44+1*B45+-1*B46+-1*B47+1*B48+1*B49+1*B50+1*B51</f>
         <v/>
       </c>
-      <c r="C52" s="21">
+      <c r="C52" s="28">
         <f>1*C22+-1*C23+1*C24+-1*C25+1*C26+-1*C27+1*C28+-1*C29+-1*C30+-1*C31+1*C32+1*C33+-1*C34+1*C35+1*C36+1*C37+1*C38+1*C39+-1*C40+-1*C41+-1*C42+1*C43+1*C44+1*C45+-1*C46+-1*C47+1*C48+1*C49+1*C50+1*C51</f>
         <v/>
       </c>
-    </row>
-    <row r="53" ht="15" customHeight="1" s="10">
-      <c r="A53" s="13" t="inlineStr">
+      <c r="D52" s="33" t="n"/>
+    </row>
+    <row r="53" ht="18" customHeight="1" s="10">
+      <c r="A53" s="25" t="inlineStr">
         <is>
           <t>Cash flows from (used in) financing activities [abstract]</t>
         </is>
       </c>
-      <c r="B53" s="20" t="n"/>
-      <c r="C53" s="20" t="n"/>
-    </row>
-    <row r="54" ht="15" customHeight="1" s="10">
-      <c r="A54" s="15" t="inlineStr">
+      <c r="B53" s="26" t="n"/>
+      <c r="C53" s="26" t="n"/>
+      <c r="D53" s="32" t="n"/>
+    </row>
+    <row r="54" ht="18" customHeight="1" s="10">
+      <c r="A54" s="27" t="inlineStr">
         <is>
           <t>Payments for principal portion of lease liability</t>
         </is>
       </c>
-      <c r="B54" s="16" t="n"/>
-      <c r="C54" s="16" t="n"/>
-    </row>
-    <row r="55" ht="15" customHeight="1" s="10">
-      <c r="A55" s="15" t="inlineStr">
+      <c r="B54" s="28" t="n"/>
+      <c r="C54" s="28" t="n"/>
+      <c r="D54" s="33" t="n"/>
+    </row>
+    <row r="55" ht="18" customHeight="1" s="10">
+      <c r="A55" s="27" t="inlineStr">
         <is>
           <t>Payments for interest portion of lease liability</t>
         </is>
       </c>
-      <c r="B55" s="16" t="n"/>
-      <c r="C55" s="16" t="n"/>
-    </row>
-    <row r="56" ht="15" customHeight="1" s="10">
-      <c r="A56" s="15" t="inlineStr">
+      <c r="B55" s="28" t="n"/>
+      <c r="C55" s="28" t="n"/>
+      <c r="D55" s="33" t="n"/>
+    </row>
+    <row r="56" ht="18" customHeight="1" s="10">
+      <c r="A56" s="27" t="inlineStr">
         <is>
           <t>Proceeds from issuing shares</t>
         </is>
       </c>
-      <c r="B56" s="16" t="n"/>
-      <c r="C56" s="16" t="n"/>
-    </row>
-    <row r="57" ht="23.85" customHeight="1" s="10">
-      <c r="A57" s="15" t="inlineStr">
+      <c r="B56" s="28" t="n"/>
+      <c r="C56" s="28" t="n"/>
+      <c r="D56" s="33" t="n"/>
+    </row>
+    <row r="57" ht="18" customHeight="1" s="10">
+      <c r="A57" s="27" t="inlineStr">
         <is>
           <t>Proceeds from issue of shares in subsidiary to non-controlling interests</t>
         </is>
       </c>
-      <c r="B57" s="16" t="n"/>
-      <c r="C57" s="16" t="n"/>
-    </row>
-    <row r="58" ht="15" customHeight="1" s="10">
-      <c r="A58" s="15" t="inlineStr">
+      <c r="B57" s="28" t="n"/>
+      <c r="C57" s="28" t="n"/>
+      <c r="D57" s="33" t="n"/>
+    </row>
+    <row r="58" ht="18" customHeight="1" s="10">
+      <c r="A58" s="27" t="inlineStr">
         <is>
           <t>Proceeds from issuing other equity instruments</t>
         </is>
       </c>
-      <c r="B58" s="16" t="n"/>
-      <c r="C58" s="16" t="n"/>
-    </row>
-    <row r="59" ht="15" customHeight="1" s="10">
-      <c r="A59" s="15" t="inlineStr">
+      <c r="B58" s="28" t="n"/>
+      <c r="C58" s="28" t="n"/>
+      <c r="D58" s="33" t="n"/>
+    </row>
+    <row r="59" ht="18" customHeight="1" s="10">
+      <c r="A59" s="27" t="inlineStr">
         <is>
           <t>Proceeds from exercise of options</t>
         </is>
       </c>
-      <c r="B59" s="16" t="n"/>
-      <c r="C59" s="16" t="n"/>
-    </row>
-    <row r="60" ht="15" customHeight="1" s="10">
-      <c r="A60" s="15" t="inlineStr">
+      <c r="B59" s="28" t="n"/>
+      <c r="C59" s="28" t="n"/>
+      <c r="D59" s="33" t="n"/>
+    </row>
+    <row r="60" ht="18" customHeight="1" s="10">
+      <c r="A60" s="27" t="inlineStr">
         <is>
           <t>Payments to acquire or redeem entity's shares</t>
         </is>
       </c>
-      <c r="B60" s="16" t="n"/>
-      <c r="C60" s="16" t="n"/>
-    </row>
-    <row r="61" ht="15" customHeight="1" s="10">
-      <c r="A61" s="15" t="inlineStr">
+      <c r="B60" s="28" t="n"/>
+      <c r="C60" s="28" t="n"/>
+      <c r="D60" s="33" t="n"/>
+    </row>
+    <row r="61" ht="18" customHeight="1" s="10">
+      <c r="A61" s="27" t="inlineStr">
         <is>
           <t>Payments made to non-controlling interests</t>
         </is>
       </c>
-      <c r="B61" s="16" t="n"/>
-      <c r="C61" s="16" t="n"/>
-    </row>
-    <row r="62" ht="15" customHeight="1" s="10">
-      <c r="A62" s="15" t="inlineStr">
+      <c r="B61" s="28" t="n"/>
+      <c r="C61" s="28" t="n"/>
+      <c r="D61" s="33" t="n"/>
+    </row>
+    <row r="62" ht="18" customHeight="1" s="10">
+      <c r="A62" s="27" t="inlineStr">
         <is>
           <t>Payments of other equity instruments</t>
         </is>
       </c>
-      <c r="B62" s="16" t="n"/>
-      <c r="C62" s="16" t="n"/>
-    </row>
-    <row r="63" ht="15" customHeight="1" s="10">
-      <c r="A63" s="15" t="inlineStr">
+      <c r="B62" s="28" t="n"/>
+      <c r="C62" s="28" t="n"/>
+      <c r="D62" s="33" t="n"/>
+    </row>
+    <row r="63" ht="18" customHeight="1" s="10">
+      <c r="A63" s="27" t="inlineStr">
         <is>
           <t>Cash payments for issuance of perpetual sukuk</t>
         </is>
       </c>
-      <c r="B63" s="16" t="n"/>
-      <c r="C63" s="16" t="n"/>
-    </row>
-    <row r="64" ht="15" customHeight="1" s="10">
-      <c r="A64" s="15" t="inlineStr">
+      <c r="B63" s="28" t="n"/>
+      <c r="C63" s="28" t="n"/>
+      <c r="D63" s="33" t="n"/>
+    </row>
+    <row r="64" ht="18" customHeight="1" s="10">
+      <c r="A64" s="27" t="inlineStr">
         <is>
           <t>Proceeds from issue of bonds, notes and debentures</t>
         </is>
       </c>
-      <c r="B64" s="16" t="n"/>
-      <c r="C64" s="16" t="n"/>
-    </row>
-    <row r="65" ht="15" customHeight="1" s="10">
-      <c r="A65" s="15" t="inlineStr">
+      <c r="B64" s="28" t="n"/>
+      <c r="C64" s="28" t="n"/>
+      <c r="D64" s="33" t="n"/>
+    </row>
+    <row r="65" ht="18" customHeight="1" s="10">
+      <c r="A65" s="27" t="inlineStr">
         <is>
           <t>Repayments of borrowings</t>
         </is>
       </c>
-      <c r="B65" s="16" t="n"/>
-      <c r="C65" s="16" t="n"/>
-    </row>
-    <row r="66" ht="15" customHeight="1" s="10">
-      <c r="A66" s="15" t="inlineStr">
+      <c r="B65" s="28" t="n"/>
+      <c r="C65" s="28" t="n"/>
+      <c r="D65" s="33" t="n"/>
+    </row>
+    <row r="66" ht="18" customHeight="1" s="10">
+      <c r="A66" s="27" t="inlineStr">
         <is>
           <t>Repurchase of treasury shares</t>
         </is>
       </c>
-      <c r="B66" s="16" t="n"/>
-      <c r="C66" s="16" t="n"/>
-    </row>
-    <row r="67" ht="15" customHeight="1" s="10">
-      <c r="A67" s="15" t="inlineStr">
+      <c r="B66" s="28" t="n"/>
+      <c r="C66" s="28" t="n"/>
+      <c r="D66" s="33" t="n"/>
+    </row>
+    <row r="67" ht="18" customHeight="1" s="10">
+      <c r="A67" s="27" t="inlineStr">
         <is>
           <t>Withdrawal of bank deposits</t>
         </is>
       </c>
-      <c r="B67" s="16" t="n"/>
-      <c r="C67" s="16" t="n"/>
-    </row>
-    <row r="68" ht="15" customHeight="1" s="10">
-      <c r="A68" s="15" t="inlineStr">
+      <c r="B67" s="28" t="n"/>
+      <c r="C67" s="28" t="n"/>
+      <c r="D67" s="33" t="n"/>
+    </row>
+    <row r="68" ht="18" customHeight="1" s="10">
+      <c r="A68" s="27" t="inlineStr">
         <is>
           <t>Withdrawal of securities pledged for borrowings</t>
         </is>
       </c>
-      <c r="B68" s="16" t="n"/>
-      <c r="C68" s="16" t="n"/>
-    </row>
-    <row r="69" ht="15" customHeight="1" s="10">
-      <c r="A69" s="15" t="inlineStr">
+      <c r="B68" s="28" t="n"/>
+      <c r="C68" s="28" t="n"/>
+      <c r="D68" s="33" t="n"/>
+    </row>
+    <row r="69" ht="18" customHeight="1" s="10">
+      <c r="A69" s="27" t="inlineStr">
         <is>
           <t>Dividends paid</t>
         </is>
       </c>
-      <c r="B69" s="16" t="n"/>
-      <c r="C69" s="16" t="n"/>
-    </row>
-    <row r="70" ht="15" customHeight="1" s="10">
-      <c r="A70" s="15" t="inlineStr">
+      <c r="B69" s="28" t="n"/>
+      <c r="C69" s="28" t="n"/>
+      <c r="D69" s="33" t="n"/>
+    </row>
+    <row r="70" ht="18" customHeight="1" s="10">
+      <c r="A70" s="27" t="inlineStr">
         <is>
           <t>Interest paid</t>
         </is>
       </c>
-      <c r="B70" s="16" t="n"/>
-      <c r="C70" s="16" t="n"/>
-    </row>
-    <row r="71" ht="15" customHeight="1" s="10">
-      <c r="A71" s="15" t="inlineStr">
+      <c r="B70" s="28" t="n"/>
+      <c r="C70" s="28" t="n"/>
+      <c r="D70" s="33" t="n"/>
+    </row>
+    <row r="71" ht="18" customHeight="1" s="10">
+      <c r="A71" s="27" t="inlineStr">
         <is>
           <t>Other inflows (outflows) of cash, classified as financing activities</t>
         </is>
       </c>
-      <c r="B71" s="16" t="n"/>
-      <c r="C71" s="16" t="n"/>
-    </row>
-    <row r="72" ht="15" customHeight="1" s="10">
-      <c r="A72" s="15" t="inlineStr">
+      <c r="B71" s="28" t="n"/>
+      <c r="C71" s="28" t="n"/>
+      <c r="D71" s="33" t="n"/>
+    </row>
+    <row r="72" ht="18" customHeight="1" s="10">
+      <c r="A72" s="27" t="inlineStr">
         <is>
           <t>Net cash flows from (used in) financing activities</t>
         </is>
       </c>
-      <c r="B72" s="21">
+      <c r="B72" s="28">
         <f>-1*B54+-1*B55+1*B56+1*B57+1*B58+1*B59+-1*B60+-1*B61+-1*B62+-1*B63+1*B64+-1*B65+-1*B66+1*B67+1*B68+-1*B69+-1*B70+1*B71</f>
         <v/>
       </c>
-      <c r="C72" s="21">
+      <c r="C72" s="28">
         <f>-1*C54+-1*C55+1*C56+1*C57+1*C58+1*C59+-1*C60+-1*C61+-1*C62+-1*C63+1*C64+-1*C65+-1*C66+1*C67+1*C68+-1*C69+-1*C70+1*C71</f>
         <v/>
       </c>
-    </row>
-    <row r="73" ht="23.85" customHeight="1" s="10">
-      <c r="A73" s="15" t="inlineStr">
+      <c r="D72" s="33" t="n"/>
+    </row>
+    <row r="73" ht="18" customHeight="1" s="10">
+      <c r="A73" s="27" t="inlineStr">
         <is>
           <t>Net increase (decrease) in cash and cash equivalents before effect of exchange rate changes</t>
         </is>
       </c>
-      <c r="B73" s="21">
+      <c r="B73" s="28">
         <f>1*B20+1*B52+1*B72</f>
         <v/>
       </c>
-      <c r="C73" s="21">
+      <c r="C73" s="28">
         <f>1*C20+1*C52+1*C72</f>
         <v/>
       </c>
-    </row>
-    <row r="74" ht="15" customHeight="1" s="10">
-      <c r="A74" s="15" t="inlineStr">
+      <c r="D73" s="33" t="n"/>
+    </row>
+    <row r="74" ht="18" customHeight="1" s="10">
+      <c r="A74" s="27" t="inlineStr">
         <is>
           <t>Effect of exchange rate changes on cash and cash equivalents</t>
         </is>
       </c>
-      <c r="B74" s="16" t="n"/>
-      <c r="C74" s="16" t="n"/>
-    </row>
-    <row r="75" ht="23.85" customHeight="1" s="10">
-      <c r="A75" s="15" t="inlineStr">
+      <c r="B74" s="28" t="n"/>
+      <c r="C74" s="28" t="n"/>
+      <c r="D74" s="33" t="n"/>
+    </row>
+    <row r="75" ht="18" customHeight="1" s="10">
+      <c r="A75" s="27" t="inlineStr">
         <is>
           <t>Net increase (decrease) in cash and cash equivalents after effect of exchange rate changes</t>
         </is>
       </c>
-      <c r="B75" s="21">
+      <c r="B75" s="28">
         <f>1*B73+1*B74</f>
         <v/>
       </c>
-      <c r="C75" s="21">
+      <c r="C75" s="28">
         <f>1*C73+1*C74</f>
         <v/>
       </c>
-    </row>
-    <row r="76" ht="15" customHeight="1" s="10">
-      <c r="A76" s="15" t="inlineStr">
+      <c r="D75" s="33" t="n"/>
+    </row>
+    <row r="76" ht="18" customHeight="1" s="10">
+      <c r="A76" s="27" t="inlineStr">
         <is>
           <t>Cash and cash equivalents at beginning of period</t>
         </is>
       </c>
-      <c r="B76" s="16" t="n"/>
-      <c r="C76" s="16" t="n"/>
-    </row>
-    <row r="77" ht="15" customHeight="1" s="10">
-      <c r="A77" s="15" t="inlineStr">
+      <c r="B76" s="28" t="n"/>
+      <c r="C76" s="28" t="n"/>
+      <c r="D76" s="33" t="n"/>
+    </row>
+    <row r="77" ht="18" customHeight="1" s="10">
+      <c r="A77" s="27" t="inlineStr">
         <is>
           <t>Cash and cash equivalents at end of period</t>
         </is>
       </c>
-      <c r="B77" s="21">
+      <c r="B77" s="28">
         <f>1*B76+1*B75</f>
         <v/>
       </c>
-      <c r="C77" s="21">
+      <c r="C77" s="28">
         <f>1*C76+1*C75</f>
         <v/>
       </c>
-    </row>
-    <row r="78" ht="15" customHeight="1" s="10">
-      <c r="A78" s="13" t="inlineStr">
+      <c r="D77" s="33" t="n"/>
+    </row>
+    <row r="78" ht="18" customHeight="1" s="10">
+      <c r="A78" s="25" t="inlineStr">
         <is>
           <t>Details of cash flows [abstract]</t>
         </is>
       </c>
-      <c r="B78" s="20" t="n"/>
-      <c r="C78" s="20" t="n"/>
-    </row>
-    <row r="79" ht="15" customHeight="1" s="10">
-      <c r="A79" s="17" t="inlineStr">
+      <c r="B78" s="26" t="n"/>
+      <c r="C78" s="26" t="n"/>
+      <c r="D78" s="32" t="n"/>
+    </row>
+    <row r="79" ht="18" customHeight="1" s="10">
+      <c r="A79" s="29" t="inlineStr">
         <is>
           <t>Total Cash and bank balances</t>
         </is>
       </c>
-      <c r="B79" s="18" t="n"/>
-      <c r="C79" s="18" t="n"/>
-    </row>
-    <row r="80" ht="15" customHeight="1" s="10">
-      <c r="A80" s="15" t="inlineStr">
+      <c r="B79" s="30" t="n"/>
+      <c r="C79" s="30" t="n"/>
+      <c r="D79" s="34" t="n"/>
+    </row>
+    <row r="80" ht="18" customHeight="1" s="10">
+      <c r="A80" s="27" t="inlineStr">
         <is>
           <t>Bank overdrafts</t>
         </is>
       </c>
-      <c r="B80" s="16" t="n"/>
-      <c r="C80" s="16" t="n"/>
-    </row>
-    <row r="81" ht="15" customHeight="1" s="10">
-      <c r="A81" s="15" t="inlineStr">
+      <c r="B80" s="28" t="n"/>
+      <c r="C80" s="28" t="n"/>
+      <c r="D80" s="33" t="n"/>
+    </row>
+    <row r="81" ht="18" customHeight="1" s="10">
+      <c r="A81" s="27" t="inlineStr">
         <is>
           <t>Other adjustments to reconcile cash and cash equivalents</t>
         </is>
       </c>
-      <c r="B81" s="16" t="n"/>
-      <c r="C81" s="16" t="n"/>
-    </row>
-    <row r="82" ht="15" customHeight="1" s="10">
-      <c r="A82" s="17" t="inlineStr">
+      <c r="B81" s="28" t="n"/>
+      <c r="C81" s="28" t="n"/>
+      <c r="D81" s="33" t="n"/>
+    </row>
+    <row r="82" ht="18" customHeight="1" s="10">
+      <c r="A82" s="29" t="inlineStr">
         <is>
           <t>Total cash and cash equivalents</t>
         </is>
       </c>
-      <c r="B82" s="18">
+      <c r="B82" s="30">
         <f>1*B79+-1*B80+1*B81</f>
         <v/>
       </c>
-      <c r="C82" s="18">
+      <c r="C82" s="30">
         <f>1*C79+-1*C80+1*C81</f>
         <v/>
       </c>
+      <c r="D82" s="34" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
